--- a/4th SEM/Database Management System/Homework/Normalization.xlsx
+++ b/4th SEM/Database Management System/Homework/Normalization.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="31">
   <si>
     <t xml:space="preserve">Order_id</t>
   </si>
@@ -94,10 +94,25 @@
     <t xml:space="preserve">For 1NF</t>
   </si>
   <si>
+    <t xml:space="preserve">Remove atomicity</t>
+  </si>
+  <si>
     <t xml:space="preserve">for 2NF</t>
   </si>
   <si>
+    <t xml:space="preserve">Remove partial dependency</t>
+  </si>
+  <si>
     <t xml:space="preserve">for 3NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove transitive functioonal dependency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for BCNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove non-trivial functional dependency</t>
   </si>
 </sst>
 </file>
@@ -107,11 +122,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -133,15 +149,47 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +214,18 @@
         <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA6A6"/>
+        <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF069A2E"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -208,40 +268,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -265,7 +369,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF069A2E"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -293,7 +397,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFA6A6"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -428,581 +532,1072 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.6" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="E2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="n">
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="n">
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="E5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="F6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="B8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="E9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="E10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="E12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="F13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>24</v>
+      <c r="A14" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="F15" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>3</v>
+      <c r="J15" s="7" t="s">
+        <v>1</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
+      <c r="N15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="G16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="I16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="n">
+      <c r="L16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+    <row r="17" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="G17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="8" t="n">
         <v>102</v>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="7" t="n">
+      <c r="L17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>80</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
+    <row r="18" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="G18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="I18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="7" t="n">
+      <c r="L18" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="7" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="G19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7" t="n">
+      <c r="L19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="8" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="7" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="G20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="I20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="L20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="0"/>
+      <c r="K22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="0"/>
+      <c r="K23" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="15" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="0"/>
+      <c r="K24" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="15" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="0"/>
+      <c r="K25" s="15" t="n">
+        <v>103</v>
+      </c>
+      <c r="L25" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="N25" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="0"/>
+      <c r="K26" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="L26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="L20" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="7" t="n">
+    </row>
+    <row r="27" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="0"/>
+      <c r="K27" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="L27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="15" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>25</v>
-      </c>
+    <row r="28" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="0"/>
+      <c r="K29" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="M29" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="P29" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="0"/>
+      <c r="K30" s="19" t="n">
+        <v>101</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="0"/>
+      <c r="K31" s="19" t="n">
+        <v>102</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="N31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="19" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="0"/>
+      <c r="K32" s="19" t="n">
+        <v>103</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="0"/>
+      <c r="K33" s="19" t="n">
+        <v>101</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" s="19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D34" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="0"/>
+      <c r="K34" s="19" t="n">
+        <v>101</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O34" s="19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P22:R22"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="ab@gmail.com"/>
     <hyperlink ref="H3" r:id="rId2" display="cd@gmail.com"/>
@@ -1017,6 +1612,12 @@
     <hyperlink ref="B16" r:id="rId11" display="ab@gmail.com"/>
     <hyperlink ref="B17" r:id="rId12" display="cd@gmail.com"/>
     <hyperlink ref="B18" r:id="rId13" display="ef@gmail.com"/>
+    <hyperlink ref="B23" r:id="rId14" display="ab@gmail.com"/>
+    <hyperlink ref="B24" r:id="rId15" display="cd@gmail.com"/>
+    <hyperlink ref="B25" r:id="rId16" display="ef@gmail.com"/>
+    <hyperlink ref="B30" r:id="rId17" display="ab@gmail.com"/>
+    <hyperlink ref="B31" r:id="rId18" display="cd@gmail.com"/>
+    <hyperlink ref="B32" r:id="rId19" display="ef@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
